--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,139 +5923,139 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
         <v>46126.65625</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,139 +6120,139 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>4.28</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
         <v>46126.65625</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,139 +6317,139 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="Q30" t="n">
         <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,137 +6510,137 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD34" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AE34" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AI34" t="n">
-        <v>8</v>
+        <v>6.93</v>
       </c>
       <c r="AJ34" t="n">
         <v>1.06</v>
       </c>
       <c r="AK34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL34" t="n">
         <v>1.92</v>
       </c>
-      <c r="AL34" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AM34" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AN34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP34" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.24</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.53</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.11</v>
+        <v>1.32</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46126.65625</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,137 +7298,137 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S35" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="V35" t="n">
         <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="X35" t="n">
         <v>2.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>6.85</v>
+        <v>8</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AU35" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.79</v>
+        <v>2.3</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.83</v>
+        <v>4.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.98</v>
+        <v>3.59</v>
       </c>
       <c r="R37" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.66666666666</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="R38" t="n">
-        <v>4.71</v>
+        <v>3.75</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,139 +8090,139 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.59</v>
+        <v>4.65</v>
       </c>
       <c r="R39" t="n">
-        <v>1.91</v>
+        <v>4.71</v>
       </c>
       <c r="S39" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI40"/>
+  <dimension ref="A1:BI42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1339,27 +1339,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46126.4375</v>
+        <v>46126.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46126.45833333334</v>
+        <v>46126.4375</v>
       </c>
     </row>
     <row r="8">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46126.49652777778</v>
+        <v>46126.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46126.5</v>
+        <v>46126.49652777778</v>
       </c>
     </row>
     <row r="12">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46126.54166666666</v>
+        <v>46126.5</v>
       </c>
     </row>
     <row r="16">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46126.54166666666</v>
+        <v>46126.51041666666</v>
       </c>
     </row>
     <row r="17">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46126.5625</v>
+        <v>46126.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3949,137 +3949,137 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46126.57291666666</v>
+        <v>46126.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46126.58333333334</v>
+        <v>46126.5625</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4343,137 +4343,137 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN20" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY20" t="n">
         <v>1.43</v>
       </c>
-      <c r="W20" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>2.2</v>
+        <v>1.14</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.85</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46126.58333333334</v>
+        <v>46126.57291666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46126.59375</v>
+        <v>46126.58333333334</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46126.60416666666</v>
+        <v>46126.58333333334</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46126.625</v>
+        <v>46126.59375</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46126.625</v>
+        <v>46126.60416666666</v>
       </c>
     </row>
     <row r="25">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46126.65625</v>
+        <v>46126.625</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46126.65625</v>
+        <v>46126.625</v>
       </c>
     </row>
     <row r="28">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE28" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="AF28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU28" t="n">
         <v>3.05</v>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
         <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>4.28</v>
+        <v>3.05</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,139 +6317,139 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>2.75</v>
+        <v>4.28</v>
       </c>
       <c r="S30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,137 +6510,137 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,143 +7101,143 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.8</v>
+        <v>2.97</v>
       </c>
       <c r="Q34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG34" t="n">
         <v>3.5</v>
       </c>
-      <c r="R34" t="n">
+      <c r="AH34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU34" t="n">
         <v>4</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T34" t="n">
+      <c r="AV34" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW34" t="n">
         <v>2.1</v>
       </c>
-      <c r="U34" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT34" t="n">
+      <c r="AX34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD34" t="n">
         <v>3.44</v>
       </c>
-      <c r="AU34" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>3.68</v>
-      </c>
       <c r="BE34" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46126.65625</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,142 +7696,142 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="S37" t="n">
-        <v>4.91</v>
+        <v>2.38</v>
       </c>
       <c r="T37" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="U37" t="n">
-        <v>2.4</v>
+        <v>5.08</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W37" t="n">
-        <v>2.57</v>
+        <v>2.93</v>
       </c>
       <c r="X37" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Z37" t="n">
-        <v>8.1</v>
+        <v>6.75</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG37" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AH37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM37" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI37" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AN37" t="n">
-        <v>1.2</v>
+        <v>1.94</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.27</v>
+        <v>2.51</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.02</v>
+        <v>3.44</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.46</v>
+        <v>3.07</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="BH37" t="n">
-        <v>1.53</v>
+        <v>2.55</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46126.66666666666</v>
+        <v>46126.65625</v>
       </c>
     </row>
     <row r="38">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,142 +7893,142 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.83</v>
+        <v>2.47</v>
       </c>
       <c r="Q38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD38" t="n">
         <v>3.98</v>
       </c>
-      <c r="R38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0</v>
-      </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46126.66666666666</v>
+        <v>46126.65625</v>
       </c>
     </row>
     <row r="39">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,145 +8283,539 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BI40" s="3" t="n">
+        <v>46126.66666666666</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" s="3" t="n">
+        <v>46126.66666666666</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Slovenia PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Domžale</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Radomlje</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
           <t>canceled</t>
         </is>
       </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI40" s="3" t="n">
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" s="3" t="n">
         <v>46126.875</v>
       </c>
     </row>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,137 +5919,137 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V28" t="n">
         <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="X28" t="n">
         <v>2.95</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB28" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY28" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD28" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE28" t="n">
+      <c r="AZ28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA28" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF28" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
+      <c r="BB28" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC28" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="Q29" t="n">
         <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>3.05</v>
+        <v>4.28</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,139 +6317,139 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,139 +6711,139 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,137 +7101,137 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R34" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S34" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,139 +8090,139 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.56</v>
+        <v>4.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.65</v>
+        <v>3.59</v>
       </c>
       <c r="R39" t="n">
-        <v>4.71</v>
+        <v>1.91</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,139 +8287,139 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.59</v>
+        <v>4.65</v>
       </c>
       <c r="R40" t="n">
-        <v>1.91</v>
+        <v>4.71</v>
       </c>
       <c r="S40" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,137 +5919,137 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,139 +6120,139 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.82</v>
+        <v>2.47</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>4.28</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI29" s="3" t="n">
         <v>46126.65625</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,139 +6317,139 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,139 +6711,139 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.47</v>
+        <v>1.8</v>
       </c>
       <c r="Q32" t="n">
         <v>3.5</v>
       </c>
       <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA32" t="n">
         <v>2.75</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL32" t="n">
+      <c r="BB32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC32" t="n">
         <v>2.15</v>
       </c>
-      <c r="AM32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BD32" t="n">
-        <v>3.98</v>
+        <v>3.68</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG32" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BH32" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R35" t="n">
-        <v>2.15</v>
+        <v>4.28</v>
       </c>
       <c r="S35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,137 +7692,137 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R9" t="n">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,139 +6120,139 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
         <v>46126.65625</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,139 +6514,139 @@
         </is>
       </c>
       <c r="P31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD31" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AE31" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AI31" t="n">
-        <v>8</v>
+        <v>6.93</v>
       </c>
       <c r="AJ31" t="n">
         <v>1.06</v>
       </c>
       <c r="AK31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL31" t="n">
         <v>1.92</v>
       </c>
-      <c r="AL31" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AM31" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AN31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP31" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.24</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.53</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.11</v>
+        <v>1.32</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,139 +6711,139 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="Q32" t="n">
         <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,137 +7298,137 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.82</v>
+        <v>2.97</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>4.28</v>
+        <v>2.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,143 +7692,143 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S37" t="n">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="T37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG37" t="n">
         <v>2</v>
       </c>
-      <c r="U37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>0</v>
-      </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="R40" t="n">
-        <v>4.71</v>
+        <v>3.75</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="R41" t="n">
-        <v>3.75</v>
+        <v>4.71</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI42"/>
+  <dimension ref="A1:BI43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,12 +945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46126.375</v>
+        <v>46126.33333333334</v>
       </c>
     </row>
     <row r="4">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46126.41666666666</v>
+        <v>46126.375</v>
       </c>
     </row>
     <row r="5">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1536,27 +1536,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46126.4375</v>
+        <v>46126.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,139 +5923,139 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R28" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2.36</v>
-      </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI28" s="3" t="n">
         <v>46126.65625</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="R30" t="n">
-        <v>4.28</v>
+        <v>2.36</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,139 +6514,139 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="S31" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U31" t="n">
-        <v>5.08</v>
+        <v>2.76</v>
       </c>
       <c r="V31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="X31" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>6.93</v>
+        <v>8</v>
       </c>
       <c r="AJ31" t="n">
         <v>1.06</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.53</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.32</v>
+        <v>2.11</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,137 +6707,137 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.26</v>
+        <v>2.97</v>
       </c>
       <c r="Q32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG32" t="n">
         <v>3.5</v>
       </c>
-      <c r="R32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R33" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,137 +7298,137 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.97</v>
+        <v>2.26</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="S35" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,139 +7499,139 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>4</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD36" t="n">
         <v>3.3</v>
       </c>
-      <c r="R36" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R37" t="n">
-        <v>2.75</v>
+        <v>4.28</v>
       </c>
       <c r="S37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,139 +8090,139 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,139 +8287,139 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.83</v>
+        <v>4.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.98</v>
+        <v>3.59</v>
       </c>
       <c r="R40" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,145 +8677,342 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="R42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" s="3" t="n">
+        <v>46126.66666666666</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Slovenia PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Domžale</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Radomlje</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
           <t>canceled</t>
         </is>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI42" s="3" t="n">
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" s="3" t="n">
         <v>46126.875</v>
       </c>
     </row>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,139 +5923,139 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
         <v>46126.65625</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,143 +6510,143 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD31" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AE31" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AI31" t="n">
-        <v>8</v>
+        <v>6.93</v>
       </c>
       <c r="AJ31" t="n">
         <v>1.06</v>
       </c>
       <c r="AK31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL31" t="n">
         <v>1.92</v>
       </c>
-      <c r="AL31" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AM31" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AN31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP31" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.24</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.53</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.11</v>
+        <v>1.32</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,137 +6707,137 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S32" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="R34" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.26</v>
+        <v>1.82</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R35" t="n">
-        <v>2.9</v>
+        <v>4.28</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,139 +7499,139 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="S36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>4.28</v>
+        <v>2.15</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT38" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,139 +8090,139 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,139 +8287,139 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="R40" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="S40" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.97</v>
+        <v>1.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>2.3</v>
+        <v>4.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,143 +6510,143 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE34" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="AF34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU34" t="n">
         <v>3.05</v>
       </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,143 +7495,143 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U37" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R37" t="n">
+      <c r="V37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL37" t="n">
         <v>2.15</v>
       </c>
-      <c r="S37" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y37" t="n">
+      <c r="AM37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z37" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AR37" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.28</v>
+        <v>3.98</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.47</v>
+        <v>1.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R38" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="S38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,139 +8090,139 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="R39" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="S39" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,139 +8287,139 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.83</v>
+        <v>4.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.98</v>
+        <v>3.59</v>
       </c>
       <c r="R40" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="R30" t="n">
-        <v>4.28</v>
+        <v>2.36</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,139 +6711,139 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S32" t="n">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="T32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG32" t="n">
         <v>2</v>
       </c>
-      <c r="U32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>2.39</v>
+        <v>3.95</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R34" t="n">
-        <v>2.15</v>
+        <v>4.28</v>
       </c>
       <c r="S34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,143 +7495,143 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.8</v>
+        <v>2.97</v>
       </c>
       <c r="Q36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG36" t="n">
         <v>3.5</v>
       </c>
-      <c r="R36" t="n">
+      <c r="AH36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU36" t="n">
         <v>4</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T36" t="n">
+      <c r="AV36" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW36" t="n">
         <v>2.1</v>
       </c>
-      <c r="U36" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT36" t="n">
+      <c r="AX36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD36" t="n">
         <v>3.44</v>
       </c>
-      <c r="AU36" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>3.68</v>
-      </c>
       <c r="BE36" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R37" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="S37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,143 +7889,143 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="R39" t="n">
-        <v>3.75</v>
+        <v>4.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,139 +8287,139 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="R40" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="S40" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,139 +8484,139 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R9" t="n">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,139 +6317,139 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R30" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R30" t="n">
-        <v>2.36</v>
-      </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,139 +6711,139 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R32" t="n">
-        <v>2.75</v>
+        <v>4.28</v>
       </c>
       <c r="S32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
         <v>3.52</v>
       </c>
       <c r="R34" t="n">
-        <v>4.28</v>
+        <v>3.05</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="S35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="R40" t="n">
-        <v>3.75</v>
+        <v>4.71</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>2.15</v>
+        <v>4.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>2.39</v>
+        <v>3.95</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,139 +6317,139 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,139 +6514,139 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.89</v>
+        <v>2.47</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>4.28</v>
+        <v>2.15</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="R34" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S36" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,143 +7692,143 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA37" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q37" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>0</v>
-      </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,143 +7889,143 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="Q38" t="n">
         <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="S38" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="R40" t="n">
-        <v>4.71</v>
+        <v>3.75</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,139 +8484,139 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,139 +8681,139 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.83</v>
+        <v>4.24</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.98</v>
+        <v>3.59</v>
       </c>
       <c r="R42" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R29" t="n">
-        <v>3.95</v>
+        <v>2.36</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>2.39</v>
+        <v>3.05</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,139 +6514,139 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>4.28</v>
       </c>
       <c r="S31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD32" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AE32" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AI32" t="n">
-        <v>8</v>
+        <v>6.93</v>
       </c>
       <c r="AJ32" t="n">
         <v>1.06</v>
       </c>
       <c r="AK32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL32" t="n">
         <v>1.92</v>
       </c>
-      <c r="AL32" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AM32" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AN32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP32" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.24</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.53</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.11</v>
+        <v>1.32</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.97</v>
+        <v>1.89</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>3.95</v>
       </c>
       <c r="S33" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,143 +7692,143 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="S37" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="T37" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U37" t="n">
-        <v>5.08</v>
+        <v>2.76</v>
       </c>
       <c r="V37" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W37" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="X37" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="AE37" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AI37" t="n">
-        <v>6.93</v>
+        <v>8</v>
       </c>
       <c r="AJ37" t="n">
         <v>1.06</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.53</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.32</v>
+        <v>2.11</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="Q38" t="n">
         <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,139 +8484,139 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,139 +8681,139 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.59</v>
+        <v>4.65</v>
       </c>
       <c r="R42" t="n">
-        <v>1.91</v>
+        <v>4.71</v>
       </c>
       <c r="S42" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="Q30" t="n">
         <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>3.05</v>
+        <v>4.28</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,139 +6514,139 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>2.47</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>4.28</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ33" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R35" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S35" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="S37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="S38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,143 +8283,143 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.83</v>
+        <v>4.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.98</v>
+        <v>3.59</v>
       </c>
       <c r="R40" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,139 +8484,139 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.59</v>
+        <v>4.65</v>
       </c>
       <c r="R41" t="n">
-        <v>1.91</v>
+        <v>4.71</v>
       </c>
       <c r="S41" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="R42" t="n">
-        <v>4.71</v>
+        <v>3.75</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>4.28</v>
+        <v>2.15</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.97</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R34" t="n">
-        <v>2.15</v>
+        <v>4.28</v>
       </c>
       <c r="S34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="R35" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,143 +7889,143 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD38" t="n">
         <v>3.3</v>
       </c>
-      <c r="R38" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,143 +8283,143 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="R41" t="n">
-        <v>4.71</v>
+        <v>3.75</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,143 +8677,143 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.83</v>
+        <v>4.24</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.98</v>
+        <v>3.59</v>
       </c>
       <c r="R42" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R9" t="n">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,143 +6116,143 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI29" s="3" t="n">
         <v>46126.65625</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,139 +6514,139 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
         <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="S31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,139 +6908,139 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="Q33" t="n">
         <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46126.65625</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R36" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="R37" t="n">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,143 +7889,143 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>2.39</v>
       </c>
       <c r="S38" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,143 +8283,143 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,143 +8677,143 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.59</v>
+        <v>4.65</v>
       </c>
       <c r="R42" t="n">
-        <v>1.91</v>
+        <v>4.71</v>
       </c>
       <c r="S42" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,139 +5923,139 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI28" s="3" t="n">
         <v>46126.65625</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,143 +6116,143 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>4.28</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
         <v>46126.65625</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="S30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,143 +6510,143 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" t="n">
         <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S32" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="V32" t="n">
         <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="X32" t="n">
         <v>2.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.85</v>
+        <v>8</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AU32" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.79</v>
+        <v>2.3</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,139 +6908,139 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="S33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46126.65625</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="R35" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q36" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R36" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R38" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,139 +5923,139 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
         <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
         <v>46126.65625</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,143 +6116,143 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI29" s="3" t="n">
         <v>46126.65625</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,143 +6510,143 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>2.47</v>
       </c>
       <c r="Q31" t="n">
         <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U31" t="n">
-        <v>5.08</v>
+        <v>3.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="X31" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.75</v>
+        <v>6.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="AE31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG31" t="n">
         <v>2</v>
       </c>
-      <c r="AF31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BH31" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="T32" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V32" t="n">
         <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="X32" t="n">
         <v>2.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY32" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD32" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE32" t="n">
+      <c r="AZ32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA32" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
+      <c r="BB32" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC32" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="Q35" t="n">
         <v>3.52</v>
       </c>
       <c r="R35" t="n">
-        <v>3.05</v>
+        <v>4.28</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S36" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.89</v>
+        <v>2.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>3.95</v>
+        <v>2.39</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,143 +8283,143 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="R40" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="S40" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,143 +8480,143 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.83</v>
+        <v>4.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.98</v>
+        <v>3.59</v>
       </c>
       <c r="R41" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.56</v>
+        <v>12.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.83</v>
+        <v>6.2</v>
       </c>
       <c r="R14" t="n">
-        <v>2.73</v>
+        <v>1.17</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6116,143 +6116,143 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>2.39</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
         <v>46126.65625</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,143 +6313,143 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,139 +6514,139 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.97</v>
+        <v>1.82</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R32" t="n">
-        <v>2.3</v>
+        <v>4.28</v>
       </c>
       <c r="S32" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,139 +6908,139 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U33" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="V33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL33" t="n">
         <v>2.15</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="AM33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ33" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z33" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AR33" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.28</v>
+        <v>3.98</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46126.65625</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.82</v>
+        <v>2.97</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>4.28</v>
+        <v>2.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE36" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R36" t="n">
+      <c r="AF36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU36" t="n">
         <v>3.05</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="R38" t="n">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,143 +8283,143 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.83</v>
+        <v>4.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.98</v>
+        <v>3.59</v>
       </c>
       <c r="R40" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,143 +8480,143 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="R41" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="S41" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>12.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.83</v>
+        <v>6.2</v>
       </c>
       <c r="R13" t="n">
-        <v>2.73</v>
+        <v>1.17</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>12.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>1.17</v>
+        <v>2.8</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,139 +6120,139 @@
         </is>
       </c>
       <c r="P29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT29" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI29" s="3" t="n">
         <v>46126.65625</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,143 +6313,143 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>2.39</v>
       </c>
       <c r="S30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,143 +6510,143 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA31" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="R32" t="n">
-        <v>4.28</v>
+        <v>2.36</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,139 +6908,139 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R33" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46126.65625</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S35" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="V35" t="n">
         <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="X35" t="n">
         <v>2.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>6.85</v>
+        <v>8</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AU35" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.79</v>
+        <v>2.3</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="S36" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,143 +8086,143 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,143 +8283,143 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="R41" t="n">
-        <v>3.75</v>
+        <v>4.71</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="R42" t="n">
-        <v>4.71</v>
+        <v>3.75</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>12.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>2.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>12.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8</v>
+        <v>1.17</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,139 +6120,139 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.47</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
         <v>46126.65625</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,143 +6510,143 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>4.28</v>
       </c>
       <c r="S31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA32" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,139 +6908,139 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46126.65625</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S34" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="S35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>4.28</v>
+        <v>2.36</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,143 +8086,143 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="R39" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="S39" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,143 +8283,143 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="R42" t="n">
-        <v>3.75</v>
+        <v>4.71</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R10" t="n">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>12.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>1.17</v>
+        <v>2.8</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>12.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.83</v>
+        <v>6.2</v>
       </c>
       <c r="R15" t="n">
-        <v>2.73</v>
+        <v>1.17</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>3.95</v>
+        <v>4.28</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>4.28</v>
+        <v>2.39</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>2.47</v>
       </c>
       <c r="Q32" t="n">
         <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U32" t="n">
-        <v>5.08</v>
+        <v>3.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="X32" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.75</v>
+        <v>6.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="AE32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG32" t="n">
         <v>2</v>
       </c>
-      <c r="AF32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BH32" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,139 +6908,139 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46126.65625</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R34" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S36" t="n">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="T36" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V36" t="n">
         <v>1.4</v>
       </c>
       <c r="W36" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="X36" t="n">
         <v>2.95</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z36" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY36" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD36" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE36" t="n">
+      <c r="AZ36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA36" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
+      <c r="BB36" t="n">
         <v>1.24</v>
       </c>
-      <c r="AQ36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC36" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,143 +7889,143 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="S38" t="n">
-        <v>3.41</v>
+        <v>2.38</v>
       </c>
       <c r="T38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE38" t="n">
         <v>2</v>
       </c>
-      <c r="U38" t="n">
+      <c r="AF38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA38" t="n">
         <v>2.75</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR38" t="n">
+      <c r="BB38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BG38" t="n">
         <v>1.67</v>
       </c>
-      <c r="AS38" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>0</v>
-      </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>12.4</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.2</v>
+        <v>2.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.17</v>
+        <v>2.73</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA30" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.65</v>
+        <v>1.89</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>2.39</v>
+        <v>3.95</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,139 +6711,139 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="S32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X32" t="n">
         <v>2.95</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.48</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.05</v>
+        <v>8.5</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" t="n">
+      <c r="AK32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN32" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD32" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM32" t="n">
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY32" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AZ32" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.98</v>
+        <v>3.28</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="BG32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,143 +7298,143 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="Q35" t="n">
         <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46126.65625</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,139 +7499,139 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S36" t="n">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="T36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG36" t="n">
         <v>2</v>
       </c>
-      <c r="U36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="S37" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,143 +7889,143 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>2.39</v>
       </c>
       <c r="S38" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="R39" t="n">
-        <v>3.75</v>
+        <v>4.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,143 +8283,143 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="R40" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="S40" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,143 +8677,143 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>4.45</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>4.45</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="Q28" t="n">
         <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>3.05</v>
+        <v>4.28</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S30" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD32" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AE32" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AI32" t="n">
-        <v>8</v>
+        <v>6.93</v>
       </c>
       <c r="AJ32" t="n">
         <v>1.06</v>
       </c>
       <c r="AK32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL32" t="n">
         <v>1.92</v>
       </c>
-      <c r="AL32" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AM32" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AN32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP32" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.24</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.53</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.11</v>
+        <v>1.32</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.82</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="R33" t="n">
-        <v>4.28</v>
+        <v>2.36</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R34" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.36</v>
-      </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46126.65625</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7298,143 +7298,143 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="S35" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="T35" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U35" t="n">
-        <v>5.08</v>
+        <v>2.76</v>
       </c>
       <c r="V35" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W35" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="X35" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="AE35" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AI35" t="n">
-        <v>6.93</v>
+        <v>8</v>
       </c>
       <c r="AJ35" t="n">
         <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AO35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.53</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.32</v>
+        <v>2.11</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46126.65625</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,139 +7499,139 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.47</v>
+        <v>1.89</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="S36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="R40" t="n">
-        <v>3.75</v>
+        <v>4.71</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,143 +8480,143 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,143 +8677,143 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="R42" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="S42" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>4.45</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>4.45</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
         <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>4.28</v>
+        <v>3.05</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>2.39</v>
+        <v>4.28</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,143 +6313,143 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>3.55</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>5.08</v>
+        <v>2.76</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="X32" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="AE32" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.93</v>
+        <v>8</v>
       </c>
       <c r="AJ32" t="n">
         <v>1.06</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AO32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.53</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.32</v>
+        <v>2.11</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,139 +7105,139 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46126.65625</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="S35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R36" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S38" t="n">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="T38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG38" t="n">
         <v>2</v>
       </c>
-      <c r="U38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>0</v>
-      </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.56</v>
+        <v>1.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="R40" t="n">
-        <v>4.71</v>
+        <v>3.75</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,143 +8480,143 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,143 +8677,143 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.83</v>
+        <v>4.24</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.98</v>
+        <v>3.59</v>
       </c>
       <c r="R42" t="n">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>3.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R10" t="n">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="R13" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>12.4</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.2</v>
+        <v>2.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.17</v>
+        <v>2.73</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>4.45</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>4.45</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.82</v>
+        <v>2.26</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>4.28</v>
+        <v>2.9</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,143 +6313,143 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,143 +6510,143 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q32" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R32" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="S32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,139 +6908,139 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="Q33" t="n">
         <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46126.65625</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.75</v>
+        <v>1.82</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="R35" t="n">
-        <v>2.36</v>
+        <v>4.28</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="R36" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="S36" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,139 +7893,139 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.47</v>
+        <v>3.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="S38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X38" t="n">
         <v>2.95</v>
       </c>
-      <c r="T38" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.48</v>
-      </c>
       <c r="Y38" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>6.05</v>
+        <v>8.5</v>
       </c>
       <c r="AA38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="n">
+      <c r="AK38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN38" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD38" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM38" t="n">
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY38" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.98</v>
+        <v>3.28</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="BG38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46126.65625</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,143 +8086,143 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.56</v>
+        <v>4.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.65</v>
+        <v>3.59</v>
       </c>
       <c r="R39" t="n">
-        <v>4.71</v>
+        <v>1.91</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,143 +8677,143 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="R42" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="S42" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,143 +6510,143 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>4.28</v>
       </c>
       <c r="S31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>6.93</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46126.65625</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD32" t="n">
         <v>3.3</v>
       </c>
-      <c r="R32" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,139 +6908,139 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
         <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46126.65625</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.82</v>
+        <v>2.47</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R35" t="n">
-        <v>4.28</v>
+        <v>2.75</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46126.65625</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>3.05</v>
+        <v>2.39</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,143 +8086,143 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.59</v>
+        <v>3.98</v>
       </c>
       <c r="R39" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="S39" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,143 +8480,143 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.56</v>
+        <v>4.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.65</v>
+        <v>3.59</v>
       </c>
       <c r="R41" t="n">
-        <v>4.71</v>
+        <v>1.91</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BD9" t="n">
         <v>3.5</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>12.4</v>
+        <v>2.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.2</v>
+        <v>2.83</v>
       </c>
       <c r="R12" t="n">
-        <v>1.17</v>
+        <v>2.73</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.2</v>
+        <v>2.45</v>
       </c>
       <c r="AE12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM12" t="n">
         <v>1.38</v>
       </c>
-      <c r="AF12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AN12" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>12.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8</v>
+        <v>1.17</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3765,40 +3765,40 @@
         <v>2.71</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE17" t="n">
         <v>1.91</v>
@@ -3807,28 +3807,28 @@
         <v>1.84</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>4.45</v>
+        <v>2.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4</v>
+        <v>4.45</v>
       </c>
       <c r="S22" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5144,124 +5144,124 @@
         <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE28" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R28" t="n">
+      <c r="AF28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU28" t="n">
         <v>3.05</v>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="R29" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="T29" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="U29" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>2.67</v>
+        <v>3.1</v>
       </c>
       <c r="X29" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z29" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AI29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6201,52 +6201,52 @@
         <v>1.24</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AR29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS29" t="n">
         <v>2.1</v>
       </c>
-      <c r="AS29" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AT29" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.11</v>
+        <v>1.66</v>
       </c>
       <c r="BA29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC29" t="n">
         <v>1.97</v>
       </c>
-      <c r="BB29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.43</v>
-      </c>
       <c r="BD29" t="n">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,22 +6317,22 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6341,106 +6341,106 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB30" t="n">
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>4.28</v>
+        <v>2.9</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>2.47</v>
       </c>
       <c r="Q32" t="n">
         <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U32" t="n">
-        <v>5.08</v>
+        <v>3.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="X32" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.75</v>
+        <v>6.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="AE32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG32" t="n">
         <v>2</v>
       </c>
-      <c r="AF32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BH32" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R33" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,143 +7101,143 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46126.65625</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,139 +7302,139 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R35" t="n">
-        <v>2.75</v>
+        <v>4.28</v>
       </c>
       <c r="S35" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="U35" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="V35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.36</v>
       </c>
-      <c r="W35" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.46</v>
-      </c>
       <c r="Z35" t="n">
-        <v>6.05</v>
+        <v>7.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM35" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD35" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM35" t="n">
+      <c r="AN35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AQ35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX35" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO35" t="n">
+      <c r="AY35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB35" t="n">
         <v>1.25</v>
       </c>
-      <c r="AP35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR35" t="n">
+      <c r="BC35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE35" t="n">
         <v>1.6</v>
       </c>
-      <c r="AS35" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BF35" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
         <v>46126.65625</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,34 +7499,34 @@
         </is>
       </c>
       <c r="P36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W36" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R36" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -7538,91 +7538,91 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB36" t="n">
         <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,143 +8283,143 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.56</v>
+        <v>4.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.65</v>
+        <v>3.59</v>
       </c>
       <c r="R40" t="n">
-        <v>4.71</v>
+        <v>1.91</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,143 +8480,143 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
-        <v>3.54</v>
+        <v>2.99</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="X10" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM10" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI10" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AN10" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,91 +2771,91 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="R12" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="S12" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL12" t="n">
         <v>1.81</v>
       </c>
-      <c r="U12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AM12" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AS12" t="n">
         <v>2.8</v>
@@ -2870,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AX12" t="n">
         <v>1.37</v>
@@ -2879,25 +2879,25 @@
         <v>1.22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.82</v>
+        <v>2.29</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -4544,19 +4544,19 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S21" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
         <v>3.31</v>
@@ -4568,91 +4568,91 @@
         <v>2.93</v>
       </c>
       <c r="X21" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.64</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="BA21" t="n">
         <v>1.85</v>
@@ -4661,10 +4661,10 @@
         <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="BE21" t="n">
         <v>1.6</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,143 +5919,143 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD28" t="n">
         <v>3.4</v>
       </c>
-      <c r="R28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.74</v>
-      </c>
       <c r="AE28" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AI28" t="n">
-        <v>8</v>
+        <v>6.93</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AM28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>1.32</v>
       </c>
-      <c r="AN28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2.11</v>
-      </c>
       <c r="BA28" t="n">
-        <v>1.97</v>
+        <v>3.68</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.43</v>
+        <v>2.06</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.28</v>
+        <v>3.68</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI28" s="3" t="n">
         <v>46126.65625</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.16</v>
-      </c>
       <c r="U29" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG29" t="n">
         <v>3.1</v>
       </c>
-      <c r="X29" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.43</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AW29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BA29" t="n">
         <v>2</v>
       </c>
-      <c r="AX29" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>2.48</v>
-      </c>
       <c r="BB29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="R30" t="n">
-        <v>2.39</v>
+        <v>4.28</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U30" t="n">
-        <v>2.85</v>
+        <v>4.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X30" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.75</v>
+        <v>2.94</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN30" t="n">
         <v>1.93</v>
       </c>
-      <c r="AG30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK30" t="n">
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>1.58</v>
       </c>
-      <c r="AL30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BA30" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,22 +6514,22 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>2.9</v>
+        <v>2.39</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6538,106 +6538,106 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB31" t="n">
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,139 +6711,139 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.47</v>
+        <v>1.89</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="S32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X32" t="n">
         <v>2.95</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.48</v>
-      </c>
       <c r="Y32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>1.46</v>
       </c>
-      <c r="Z32" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BA32" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7101,143 +7101,143 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="S34" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="T34" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U34" t="n">
-        <v>5.08</v>
+        <v>2.76</v>
       </c>
       <c r="V34" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W34" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="X34" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="AE34" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.3</v>
+        <v>4.37</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AI34" t="n">
-        <v>6.93</v>
+        <v>7.8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.94</v>
+        <v>1.42</v>
       </c>
       <c r="AO34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
         <v>1.28</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.44</v>
+        <v>2.98</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.07</v>
+        <v>3.34</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.32</v>
+        <v>2.11</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.68</v>
+        <v>3.28</v>
       </c>
       <c r="BE34" t="n">
         <v>1.63</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
         <v>46126.65625</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.82</v>
+        <v>3.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>4.28</v>
+        <v>2.1</v>
       </c>
       <c r="S35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="R36" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="S36" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="T36" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U36" t="n">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="V36" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="W36" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="X36" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AF36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>1.66</v>
       </c>
-      <c r="AG36" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BA36" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="S37" t="n">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="T37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG37" t="n">
         <v>2</v>
       </c>
-      <c r="U37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>0</v>
-      </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,139 +8090,139 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.83</v>
+        <v>4.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>3.75</v>
+        <v>1.9</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,143 +8283,143 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.59</v>
+        <v>4.65</v>
       </c>
       <c r="R40" t="n">
-        <v>1.91</v>
+        <v>4.71</v>
       </c>
       <c r="S40" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="R42" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="R17" t="n">
-        <v>2.71</v>
+        <v>2.49</v>
       </c>
       <c r="S17" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.45</v>
+        <v>2.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.45</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>2.49</v>
+        <v>2.71</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5919,143 +5919,143 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>2.97</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S28" t="n">
         <v>3.5</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU28" t="n">
         <v>4</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="AV28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA28" t="n">
         <v>2.1</v>
       </c>
-      <c r="U28" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>3.68</v>
-      </c>
       <c r="BB28" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.68</v>
+        <v>3.44</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
         <v>46126.65625</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC29" t="n">
         <v>2.36</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK29" t="n">
+      <c r="BD29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE29" t="n">
         <v>1.63</v>
       </c>
-      <c r="AL29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.82</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>4.28</v>
+        <v>2.9</v>
       </c>
       <c r="S30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,130 +6514,130 @@
         </is>
       </c>
       <c r="P31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W31" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="X31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU31" t="n">
         <v>3.2</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT31" t="n">
+      <c r="AV31" t="n">
         <v>2.38</v>
       </c>
-      <c r="AU31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AW31" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.02</v>
+        <v>1.46</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.98</v>
+        <v>3.1</v>
       </c>
       <c r="BB31" t="n">
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>4.25</v>
+        <v>5.08</v>
       </c>
       <c r="V32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.41</v>
       </c>
-      <c r="W32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BE32" t="n">
         <v>1.66</v>
       </c>
-      <c r="AG32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,22 +6908,22 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R33" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6947,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -6989,49 +6989,49 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU33" t="n">
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB33" t="n">
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q34" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R34" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="S34" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>2.02</v>
       </c>
-      <c r="U34" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>2.11</v>
-      </c>
       <c r="BA34" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="R35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL35" t="n">
         <v>2.1</v>
       </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,139 +7499,139 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="S36" t="n">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="T36" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U36" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="V36" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W36" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="X36" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA36" t="n">
         <v>1.06</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO36" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH36" t="n">
+      <c r="AP36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ36" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI36" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK36" t="n">
+      <c r="AR36" t="n">
         <v>1.6</v>
       </c>
-      <c r="AL36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AS36" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AW36" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="BF36" t="n">
         <v>1.18</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="S37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.97</v>
+        <v>1.82</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.27</v>
+        <v>3.52</v>
       </c>
       <c r="R38" t="n">
-        <v>2.3</v>
+        <v>4.28</v>
       </c>
       <c r="S38" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="U38" t="n">
-        <v>2.98</v>
+        <v>4.4</v>
       </c>
       <c r="V38" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W38" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="X38" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB38" t="n">
         <v>1.02</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AF38" t="n">
         <v>1.73</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AI38" t="n">
-        <v>6.85</v>
+        <v>6.65</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AN38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY38" t="n">
         <v>1.32</v>
       </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,139 +8090,139 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R39" t="n">
-        <v>1.9</v>
+        <v>4.67</v>
       </c>
       <c r="S39" t="n">
-        <v>4.8</v>
+        <v>2.17</v>
       </c>
       <c r="T39" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="V39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y39" t="n">
         <v>1.43</v>
       </c>
-      <c r="W39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.31</v>
-      </c>
       <c r="Z39" t="n">
-        <v>8.1</v>
+        <v>6.25</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD39" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>2.3</v>
-      </c>
       <c r="BA39" t="n">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BC39" t="n">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="BD39" t="n">
-        <v>3.2</v>
+        <v>4.35</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,139 +8681,139 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.67</v>
+        <v>4.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>4.67</v>
+        <v>1.9</v>
       </c>
       <c r="S42" t="n">
-        <v>2.17</v>
+        <v>4.8</v>
       </c>
       <c r="T42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ42" t="n">
         <v>2.3</v>
       </c>
-      <c r="U42" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W42" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR42" t="n">
+      <c r="BA42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BH42" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="S10" t="n">
-        <v>2.99</v>
+        <v>3.54</v>
       </c>
       <c r="T10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL10" t="n">
         <v>2.05</v>
       </c>
-      <c r="U10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AM10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>12.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.87</v>
+        <v>6.2</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7</v>
+        <v>1.17</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN12" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,91 +2968,91 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="R13" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="S13" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="T13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL13" t="n">
         <v>1.81</v>
       </c>
-      <c r="U13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AM13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AS13" t="n">
         <v>2.8</v>
@@ -3067,7 +3067,7 @@
         <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AX13" t="n">
         <v>1.37</v>
@@ -3076,25 +3076,25 @@
         <v>1.22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.82</v>
+        <v>2.29</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.72</v>
+        <v>1.69</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>2.42</v>
+        <v>4.45</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.69</v>
+        <v>2.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>4.45</v>
+        <v>2.42</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.97</v>
+        <v>2.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.27</v>
+        <v>3.46</v>
       </c>
       <c r="R28" t="n">
-        <v>2.3</v>
+        <v>3.02</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="T28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF28" t="n">
         <v>2</v>
       </c>
-      <c r="U28" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE28" t="n">
+      <c r="AG28" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC28" t="n">
         <v>1.97</v>
       </c>
-      <c r="AF28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD28" t="n">
-        <v>3.44</v>
+        <v>4.15</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,139 +6317,139 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,130 +6514,130 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.89</v>
+        <v>2.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>3.95</v>
+        <v>2.39</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>4.25</v>
+        <v>2.85</v>
       </c>
       <c r="V31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV31" t="n">
         <v>2.95</v>
       </c>
-      <c r="Y31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ31" t="n">
+      <c r="AW31" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY31" t="n">
         <v>1.5</v>
       </c>
-      <c r="AR31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AZ31" t="n">
-        <v>1.46</v>
+        <v>2.02</v>
       </c>
       <c r="BA31" t="n">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="BB31" t="n">
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W33" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="X33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC33" t="n">
         <v>2.2</v>
       </c>
-      <c r="U33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX33" t="n">
+      <c r="BD33" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BE33" t="n">
         <v>1.58</v>
       </c>
-      <c r="AY33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7129,106 +7129,106 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE35" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AF35" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.83</v>
+        <v>4.37</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AI35" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AJ35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BF35" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,139 +7499,139 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R36" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT36" t="n">
         <v>2.75</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V36" t="n">
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY36" t="n">
         <v>1.36</v>
       </c>
-      <c r="W36" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AZ36" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,130 +7696,130 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.4</v>
+        <v>1.89</v>
       </c>
       <c r="Q37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU37" t="n">
         <v>3.2</v>
       </c>
-      <c r="R37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0</v>
-      </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB37" t="n">
         <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF37" t="n">
         <v>0</v>
@@ -7893,22 +7893,22 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="R38" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="S38" t="n">
         <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="U38" t="n">
-        <v>4.4</v>
+        <v>5.11</v>
       </c>
       <c r="V38" t="n">
         <v>1.43</v>
@@ -7920,7 +7920,7 @@
         <v>2.99</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z38" t="n">
         <v>7.2</v>
@@ -7938,19 +7938,19 @@
         <v>2.94</v>
       </c>
       <c r="AE38" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF38" t="n">
         <v>1.73</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="AH38" t="n">
         <v>1.23</v>
       </c>
       <c r="AI38" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="AJ38" t="n">
         <v>1.05</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="R39" t="n">
-        <v>4.67</v>
+        <v>3.75</v>
       </c>
       <c r="S39" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.98</v>
+        <v>4.65</v>
       </c>
       <c r="R41" t="n">
-        <v>3.75</v>
+        <v>4.71</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>2.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="S8" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="U8" t="n">
-        <v>3.35</v>
+        <v>2.77</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="X8" t="n">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.8</v>
+        <v>5.45</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.31</v>
+        <v>3.15</v>
       </c>
       <c r="R10" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
-        <v>3.54</v>
+        <v>2.99</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="U10" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="X10" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM10" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI10" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AN10" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -3371,13 +3371,13 @@
         <v>2.73</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="T15" t="n">
         <v>1.81</v>
       </c>
       <c r="U15" t="n">
-        <v>3.95</v>
+        <v>4.12</v>
       </c>
       <c r="V15" t="n">
         <v>1.59</v>
@@ -3386,22 +3386,22 @@
         <v>2.2</v>
       </c>
       <c r="X15" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Y15" t="n">
         <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="n">
         <v>2.45</v>
@@ -3410,13 +3410,13 @@
         <v>2.84</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG15" t="n">
         <v>5.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AI15" t="n">
         <v>11.5</v>
@@ -3425,64 +3425,64 @@
         <v>1.01</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AT15" t="n">
         <v>3.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AV15" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AY15" t="n">
         <v>1.22</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BC15" t="n">
         <v>2.82</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="BE15" t="n">
         <v>1.35</v>
@@ -3953,19 +3953,19 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.82</v>
+        <v>2.51</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="S18" t="n">
         <v>3.46</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
         <v>3.25</v>
@@ -3995,13 +3995,13 @@
         <v>1.32</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AG18" t="n">
         <v>3.48</v>
@@ -4019,13 +4019,13 @@
         <v>1.8</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AM18" t="n">
         <v>1.39</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,16 +4067,16 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BD18" t="n">
         <v>3.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF18" t="n">
         <v>1.14</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.69</v>
+        <v>2.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.33</v>
+        <v>3.28</v>
       </c>
       <c r="R21" t="n">
-        <v>4.45</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.72</v>
+        <v>1.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.42</v>
+        <v>4.75</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="T22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE22" t="n">
         <v>1.94</v>
       </c>
-      <c r="U22" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH22" t="n">
+      <c r="BF22" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="R27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
         <v>2.62</v>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.23</v>
+        <v>1.89</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>3.02</v>
+        <v>3.95</v>
       </c>
       <c r="S28" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U28" t="n">
-        <v>3.35</v>
+        <v>4.25</v>
       </c>
       <c r="V28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.34</v>
       </c>
-      <c r="W28" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z28" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM28" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH28" t="n">
+      <c r="AN28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY28" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AZ28" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,143 +6313,143 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>3.2</v>
+        <v>5.08</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W30" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="X30" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.95</v>
+        <v>6.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB30" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR30" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.71</v>
       </c>
       <c r="AS30" t="n">
         <v>2.12</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.64</v>
+        <v>3.07</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.25</v>
+        <v>3.68</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="BG30" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BH30" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS31" t="n">
         <v>2.25</v>
       </c>
-      <c r="U31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA31" t="n">
+      <c r="AT31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BF31" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="S32" t="n">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U32" t="n">
-        <v>5.08</v>
+        <v>3.35</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W32" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="X32" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.75</v>
+        <v>6.15</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AE32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF32" t="n">
         <v>2</v>
       </c>
-      <c r="AF32" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG32" t="n">
-        <v>3.15</v>
+        <v>2.83</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.93</v>
+        <v>5</v>
       </c>
       <c r="AJ32" t="n">
         <v>1.09</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AN32" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AO32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.43</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AT32" t="n">
         <v>2.7</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.07</v>
+        <v>3.55</v>
       </c>
       <c r="AV32" t="n">
         <v>2.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="BA32" t="n">
-        <v>3.68</v>
+        <v>2.48</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.68</v>
+        <v>4.15</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.97</v>
+        <v>1.83</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.27</v>
+        <v>3.48</v>
       </c>
       <c r="R33" t="n">
-        <v>2.3</v>
+        <v>4.27</v>
       </c>
       <c r="S33" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="U33" t="n">
-        <v>2.98</v>
+        <v>5.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W33" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="X33" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB33" t="n">
         <v>1.02</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AF33" t="n">
         <v>1.73</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AI33" t="n">
-        <v>6.85</v>
+        <v>6.5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AN33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY33" t="n">
         <v>1.32</v>
       </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AZ33" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="R34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA34" t="n">
         <v>2.1</v>
       </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R35" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="S35" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>2.02</v>
       </c>
-      <c r="U35" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>2.11</v>
-      </c>
       <c r="BA35" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,139 +7499,139 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U36" t="n">
         <v>3.2</v>
       </c>
-      <c r="T36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W36" t="n">
         <v>3.1</v>
       </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
       <c r="X36" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AH36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM36" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI36" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AN36" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="BA36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BG36" t="n">
         <v>2</v>
       </c>
-      <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,130 +7696,130 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R37" t="n">
-        <v>3.95</v>
+        <v>2.36</v>
       </c>
       <c r="S37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
         <v>2.5</v>
       </c>
-      <c r="T37" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U37" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AW37" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="BA37" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="BB37" t="n">
         <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="BF37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="R38" t="n">
-        <v>4.27</v>
+        <v>2.1</v>
       </c>
       <c r="S38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>4.65</v>
       </c>
       <c r="R40" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="S40" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI43"/>
+  <dimension ref="A1:BI44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>12.4</v>
+        <v>2.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.2</v>
+        <v>2.83</v>
       </c>
       <c r="R12" t="n">
-        <v>1.17</v>
+        <v>2.73</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.2</v>
+        <v>2.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.38</v>
+        <v>2.84</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.98</v>
+        <v>5.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.68</v>
+        <v>1.13</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.2</v>
+        <v>11.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>3.24</v>
+        <v>3.69</v>
       </c>
       <c r="T15" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="U15" t="n">
-        <v>4.12</v>
+        <v>2.87</v>
       </c>
       <c r="V15" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2</v>
+        <v>2.86</v>
       </c>
       <c r="X15" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="AA15" t="n">
         <v>1.02</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.45</v>
+        <v>3.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.84</v>
+        <v>2.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>11.5</v>
+        <v>7.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3443,52 +3443,52 @@
         <v>1.39</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.7</v>
+        <v>4.13</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AY15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.22</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.37</v>
-      </c>
       <c r="BC15" t="n">
-        <v>2.82</v>
+        <v>2.38</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.74</v>
+        <v>3.58</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,76 +3756,76 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="S17" t="n">
-        <v>3.18</v>
+        <v>3.46</v>
       </c>
       <c r="T17" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="U17" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="W17" t="n">
-        <v>3.02</v>
+        <v>2.36</v>
       </c>
       <c r="X17" t="n">
-        <v>2.44</v>
+        <v>2.99</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.04</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AH17" t="n">
+      <c r="AK17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.39</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.25</v>
       </c>
       <c r="AN17" t="n">
         <v>1.4</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.14</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,76 +3953,76 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="S18" t="n">
-        <v>3.46</v>
+        <v>3.18</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="U18" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="V18" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>2.36</v>
+        <v>3.02</v>
       </c>
       <c r="X18" t="n">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC18" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.88</v>
+        <v>4.05</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.48</v>
+        <v>2.65</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.92</v>
+        <v>2.32</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
         <v>1.4</v>
@@ -4031,55 +4031,55 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="T20" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="U20" t="n">
-        <v>6.5</v>
+        <v>5.55</v>
       </c>
       <c r="V20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="X20" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX20" t="n">
         <v>1.65</v>
       </c>
-      <c r="AF20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AY20" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.300000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S24" t="n">
         <v>3.89</v>
@@ -5153,16 +5153,16 @@
         <v>2.98</v>
       </c>
       <c r="V24" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X24" t="n">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
         <v>7.7</v>
@@ -5180,10 +5180,10 @@
         <v>2.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG24" t="n">
         <v>3.58</v>
@@ -5201,7 +5201,7 @@
         <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AM24" t="n">
         <v>1.32</v>
@@ -5213,52 +5213,52 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AT24" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="BB24" t="n">
         <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="BD24" t="n">
         <v>3.36</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BF24" t="n">
         <v>1.11</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.17</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S26" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="U26" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="V26" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="W26" t="n">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z26" t="n">
-        <v>15</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.03</v>
+        <v>2.89</v>
       </c>
       <c r="AE26" t="n">
-        <v>3.08</v>
+        <v>2.32</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="AG26" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AI26" t="n">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.02</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BE26" t="n">
         <v>1.48</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BF26" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>3.17</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="R27" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="T27" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="U27" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="V27" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="W27" t="n">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="X27" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.300000000000001</v>
+        <v>15</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.89</v>
+        <v>2.03</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.32</v>
+        <v>3.08</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="AG27" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AI27" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="AJ27" t="n">
         <v>1.02</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AX27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BE27" t="n">
         <v>1.3</v>
       </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF27" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="R28" t="n">
-        <v>3.95</v>
+        <v>4.27</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="U28" t="n">
-        <v>4.25</v>
+        <v>5.11</v>
       </c>
       <c r="V28" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="X28" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="Y28" t="n">
         <v>1.34</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AE28" t="n">
         <v>2.07</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="AH28" t="n">
         <v>1.23</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR28" t="n">
         <v>1.87</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AS28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW28" t="n">
         <v>1.82</v>
       </c>
-      <c r="AM28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ28" t="n">
+      <c r="AX28" t="n">
         <v>1.5</v>
       </c>
-      <c r="AR28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AS28" t="n">
+      <c r="AY28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC28" t="n">
         <v>2.3</v>
       </c>
-      <c r="AT28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.28</v>
-      </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>2.97</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.5</v>
       </c>
-      <c r="R29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,40 +6317,40 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="S30" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="U30" t="n">
-        <v>5.08</v>
+        <v>4.95</v>
       </c>
       <c r="V30" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W30" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="X30" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AB30" t="n">
         <v>1.01</v>
@@ -6359,97 +6359,97 @@
         <v>1.26</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.93</v>
+        <v>6.42</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK30" t="n">
         <v>1.8</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AN30" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.12</v>
+        <v>3.34</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.7</v>
+        <v>4.99</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.07</v>
+        <v>2.37</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
         <v>46126.65625</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="T32" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>3.35</v>
+        <v>5.08</v>
       </c>
       <c r="V32" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W32" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="X32" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.15</v>
+        <v>6.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI32" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AJ32" t="n">
         <v>1.09</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AM32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AP32" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.24</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.43</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AT32" t="n">
         <v>2.7</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.55</v>
+        <v>3.07</v>
       </c>
       <c r="AV32" t="n">
         <v>2.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AZ32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BE32" t="n">
         <v>1.66</v>
       </c>
-      <c r="BA32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.72</v>
-      </c>
       <c r="BF32" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>4.27</v>
+        <v>3.95</v>
       </c>
       <c r="S33" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>5.11</v>
+        <v>4.25</v>
       </c>
       <c r="V33" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W33" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="X33" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="Y33" t="n">
         <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AE33" t="n">
         <v>2.07</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="AH33" t="n">
         <v>1.23</v>
       </c>
       <c r="AI33" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AL33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW33" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ33" t="n">
+      <c r="AX33" t="n">
         <v>1.53</v>
       </c>
-      <c r="AR33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU33" t="n">
+      <c r="AY33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BA33" t="n">
         <v>3.1</v>
       </c>
-      <c r="AV33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BB33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S34" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U34" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN34" t="n">
         <v>1.37</v>
       </c>
-      <c r="W34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC34" t="n">
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ34" t="n">
         <v>1.34</v>
       </c>
-      <c r="AD34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AR34" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AS34" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BA34" t="n">
         <v>1.98</v>
       </c>
-      <c r="AT34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BB34" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD35" t="n">
         <v>3.3</v>
       </c>
-      <c r="R35" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T35" t="n">
+      <c r="AE35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS35" t="n">
         <v>2.25</v>
       </c>
-      <c r="U35" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA35" t="n">
+      <c r="AT35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BF35" t="n">
         <v>1.09</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,118 +7499,118 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="R36" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="S36" t="n">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="T36" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U36" t="n">
-        <v>3.2</v>
+        <v>3.68</v>
       </c>
       <c r="V36" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W36" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="X36" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Y36" t="n">
         <v>1.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.95</v>
+        <v>6.15</v>
       </c>
       <c r="AA36" t="n">
         <v>1.06</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG36" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI36" t="n">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AO36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="BB36" t="n">
         <v>1.18</v>
@@ -7619,19 +7619,19 @@
         <v>1.98</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,139 +7696,139 @@
         </is>
       </c>
       <c r="P37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R37" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>3.15</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.2</v>
       </c>
       <c r="T37" t="n">
         <v>2.2</v>
       </c>
       <c r="U37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W37" t="n">
         <v>3.1</v>
       </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
       <c r="X37" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BA37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BG37" t="n">
         <v>2</v>
       </c>
-      <c r="BB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>0</v>
-      </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD38" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -7974,49 +7974,49 @@
         <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU38" t="n">
         <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB38" t="n">
         <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD38" t="n">
         <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF38" t="n">
         <v>0</v>
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,130 +8090,130 @@
         </is>
       </c>
       <c r="P39" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q39" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BB39" t="n">
         <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD39" t="n">
         <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46126.66666666666</v>
+        <v>46126.65625</v>
       </c>
     </row>
     <row r="40">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.65</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>4.71</v>
+        <v>4.67</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.67</v>
+        <v>3.64</v>
       </c>
       <c r="Q41" t="n">
+        <v>4</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S41" t="n">
         <v>3.8</v>
       </c>
-      <c r="R41" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.17</v>
-      </c>
       <c r="T41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W41" t="n">
+        <v>4</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE41" t="n">
         <v>2.3</v>
       </c>
-      <c r="U41" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W41" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ41" t="n">
+      <c r="BF41" t="n">
         <v>1.4</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>1.21</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,139 +8681,139 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q42" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA42" t="n">
         <v>3.6</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W42" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BB42" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.2</v>
+        <v>5.65</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="BG42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,145 +8874,342 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BI43" s="3" t="n">
+        <v>46126.66666666666</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Slovenia PrvaLiga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Domžale</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Radomlje</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
           <t>canceled</t>
         </is>
       </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI43" s="3" t="n">
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI44" s="3" t="n">
         <v>46126.875</v>
       </c>
     </row>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S9" t="n">
         <v>2.99</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="U9" t="n">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="X9" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AI9" t="n">
-        <v>5.45</v>
+        <v>6.8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.34</v>
+        <v>2.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="S10" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="U10" t="n">
-        <v>3.35</v>
+        <v>2.77</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="X10" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z10" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>12.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3007,40 +3007,40 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>12.4</v>
+        <v>2.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.2</v>
+        <v>2.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.17</v>
+        <v>2.73</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.2</v>
+        <v>2.45</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.38</v>
+        <v>2.84</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.98</v>
+        <v>5.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>1.13</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.2</v>
+        <v>11.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,76 +3362,76 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R15" t="n">
         <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="X15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
         <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.08</v>
+        <v>3.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.1</v>
+        <v>6.65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AN15" t="n">
         <v>1.35</v>
@@ -3446,10 +3446,10 @@
         <v>1.72</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="AT15" t="n">
         <v>4.13</v>
@@ -3470,25 +3470,25 @@
         <v>1.15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -5135,94 +5135,94 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
-        <v>3.89</v>
+        <v>3.69</v>
       </c>
       <c r="T24" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="U24" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="X24" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB24" t="n">
         <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK24" t="n">
         <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AR24" t="n">
         <v>2.18</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AT24" t="n">
         <v>3.3</v>
@@ -5231,37 +5231,37 @@
         <v>3.18</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AW24" t="n">
         <v>1.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.36</v>
+        <v>3.52</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.5</v>
+        <v>2.81</v>
       </c>
       <c r="R25" t="n">
-        <v>4.79</v>
+        <v>2.8</v>
       </c>
       <c r="S25" t="n">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="U25" t="n">
-        <v>4.7</v>
+        <v>3.78</v>
       </c>
       <c r="V25" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="W25" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="X25" t="n">
-        <v>2.21</v>
+        <v>3.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.31</v>
+        <v>1.76</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.32</v>
+        <v>1.42</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.61</v>
+        <v>2.19</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.04</v>
+        <v>2.97</v>
       </c>
       <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
         <v>2.62</v>
       </c>
-      <c r="AU25" t="n">
-        <v>4.05</v>
-      </c>
       <c r="AV25" t="n">
-        <v>2.78</v>
+        <v>1.95</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.07</v>
+        <v>1.54</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.38</v>
+        <v>2.09</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.9</v>
+        <v>1.97</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.71</v>
+        <v>2.45</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.85</v>
+        <v>3.08</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>1.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.81</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2.8</v>
+        <v>4.79</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>2.02</v>
       </c>
       <c r="T26" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="U26" t="n">
-        <v>3.78</v>
+        <v>4.7</v>
       </c>
       <c r="V26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK26" t="n">
         <v>1.53</v>
       </c>
-      <c r="W26" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE26" t="n">
+      <c r="AL26" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN26" t="n">
         <v>2.32</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY26" t="n">
         <v>1.38</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ26" t="n">
-        <v>2.09</v>
+        <v>1.38</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.97</v>
+        <v>3.9</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.45</v>
+        <v>1.71</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.08</v>
+        <v>4.85</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="R28" t="n">
-        <v>4.27</v>
+        <v>3.02</v>
       </c>
       <c r="S28" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="T28" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="U28" t="n">
-        <v>5.11</v>
+        <v>3.68</v>
       </c>
       <c r="V28" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="X28" t="n">
-        <v>2.99</v>
+        <v>2.43</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Z28" t="n">
-        <v>7.1</v>
+        <v>6.15</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.33</v>
       </c>
-      <c r="AD28" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AI28" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U29" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN29" t="n">
         <v>1.37</v>
       </c>
-      <c r="W29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AS29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BA29" t="n">
         <v>1.98</v>
       </c>
-      <c r="AT29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>2.1</v>
-      </c>
       <c r="BB29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6313,137 +6313,137 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="S30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,22 +6514,22 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="R31" t="n">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6538,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -6553,40 +6553,40 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6595,49 +6595,49 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB31" t="n">
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,143 +6707,143 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="S32" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U32" t="n">
-        <v>5.08</v>
+        <v>2.95</v>
       </c>
       <c r="V32" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="X32" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ32" t="n">
         <v>1.41</v>
       </c>
-      <c r="Z32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AR32" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AS32" t="n">
         <v>2.12</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.07</v>
+        <v>3.64</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AW32" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC32" t="n">
         <v>1.98</v>
       </c>
-      <c r="AX32" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.06</v>
-      </c>
       <c r="BD32" t="n">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BH32" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46126.65625</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG33" t="n">
         <v>3.25</v>
       </c>
-      <c r="R33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U33" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AI33" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.07</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.76</v>
+        <v>1.42</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AQ33" t="n">
         <v>1.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AT33" t="n">
         <v>2.95</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AV33" t="n">
         <v>2.38</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.46</v>
+        <v>2.11</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="R34" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>2.85</v>
+        <v>2.98</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X34" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.8</v>
+        <v>7.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AJ34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF34" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S35" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="T35" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="U35" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.34</v>
       </c>
-      <c r="W35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AI35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AN35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX35" t="n">
         <v>1.42</v>
       </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AY35" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,143 +7495,143 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>3.02</v>
+        <v>4</v>
       </c>
       <c r="S36" t="n">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="T36" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U36" t="n">
-        <v>3.68</v>
+        <v>5.08</v>
       </c>
       <c r="V36" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W36" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="X36" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.15</v>
+        <v>6.75</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI36" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AJ36" t="n">
         <v>1.09</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.43</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AT36" t="n">
         <v>2.7</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.55</v>
+        <v>3.07</v>
       </c>
       <c r="AV36" t="n">
         <v>2.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AZ36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.66</v>
       </c>
-      <c r="BA36" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BF36" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46126.65625</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,143 +7692,143 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="R37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X37" t="n">
         <v>2.75</v>
       </c>
-      <c r="S37" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.6</v>
-      </c>
       <c r="Y37" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AI37" t="n">
-        <v>5.3</v>
+        <v>6.42</v>
       </c>
       <c r="AJ37" t="n">
         <v>1.11</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BB37" t="n">
         <v>1.25</v>
       </c>
-      <c r="AP37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC37" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="BF37" t="n">
         <v>1.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46126.65625</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,130 +7893,130 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R38" t="n">
-        <v>2.36</v>
+        <v>3.95</v>
       </c>
       <c r="S38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU38" t="n">
         <v>3.2</v>
       </c>
-      <c r="T38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U38" t="n">
+      <c r="AV38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BA38" t="n">
         <v>3.1</v>
       </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>2</v>
-      </c>
       <c r="BB38" t="n">
         <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="BD38" t="n">
         <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="BF38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.39</v>
+        <v>1.83</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="R39" t="n">
-        <v>2.09</v>
+        <v>4.27</v>
       </c>
       <c r="S39" t="n">
-        <v>3.95</v>
+        <v>2.4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="U39" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W39" t="n">
         <v>2.75</v>
       </c>
-      <c r="V39" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2.63</v>
-      </c>
       <c r="X39" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="Y39" t="n">
         <v>1.34</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AE39" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG39" t="n">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="AH39" t="n">
         <v>1.23</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AM39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB39" t="n">
         <v>1.25</v>
       </c>
-      <c r="AN39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ39" t="n">
+      <c r="BC39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE39" t="n">
         <v>1.6</v>
       </c>
-      <c r="AR39" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.67</v>
+        <v>3.64</v>
       </c>
       <c r="Q40" t="n">
+        <v>4</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S40" t="n">
         <v>3.8</v>
       </c>
-      <c r="R40" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.17</v>
-      </c>
       <c r="T40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>4</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE40" t="n">
         <v>2.3</v>
       </c>
-      <c r="U40" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W40" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ40" t="n">
+      <c r="BF40" t="n">
         <v>1.4</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>1.21</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.64</v>
+        <v>2.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>4.44</v>
       </c>
       <c r="R41" t="n">
-        <v>1.84</v>
+        <v>2.51</v>
       </c>
       <c r="S41" t="n">
-        <v>3.8</v>
+        <v>2.71</v>
       </c>
       <c r="T41" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="U41" t="n">
-        <v>2.29</v>
+        <v>2.85</v>
       </c>
       <c r="V41" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W41" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="X41" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="AA41" t="n">
         <v>1.18</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AD41" t="n">
-        <v>6.45</v>
+        <v>5.75</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AF41" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.88</v>
+        <v>3.56</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.98</v>
+        <v>2.77</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8565,52 +8565,52 @@
         <v>1.12</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AU41" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AV41" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AX41" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AZ41" t="n">
-        <v>5.1</v>
+        <v>1.35</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="BB41" t="n">
         <v>1.12</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,139 +8681,139 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.33</v>
+        <v>4.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.44</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>2.51</v>
+        <v>1.9</v>
       </c>
       <c r="S42" t="n">
-        <v>2.71</v>
+        <v>4.1</v>
       </c>
       <c r="T42" t="n">
-        <v>2.72</v>
+        <v>2.14</v>
       </c>
       <c r="U42" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="V42" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="W42" t="n">
-        <v>4.7</v>
+        <v>2.75</v>
       </c>
       <c r="X42" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BA42" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z42" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BB42" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.65</v>
+        <v>3.85</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="BG42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BH42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BI42" s="3" t="n">
         <v>46126.66666666666</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,139 +8878,139 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R43" t="n">
-        <v>1.9</v>
+        <v>4.67</v>
       </c>
       <c r="S43" t="n">
-        <v>4.1</v>
+        <v>2.17</v>
       </c>
       <c r="T43" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="U43" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="V43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1.43</v>
       </c>
-      <c r="W43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.31</v>
-      </c>
       <c r="Z43" t="n">
-        <v>8.1</v>
+        <v>6.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AG43" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AI43" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AK43" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL43" t="n">
         <v>2</v>
       </c>
-      <c r="AL43" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AM43" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.22</v>
+        <v>2.12</v>
       </c>
       <c r="AO43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AZ43" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.85</v>
+        <v>4.35</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="BG43" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BH43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
         <v>46126.66666666666</v>

--- a/jogos_2026-04-14.xlsx
+++ b/jogos_2026-04-14.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>